--- a/output/MarketNews-202603.xlsx
+++ b/output/MarketNews-202603.xlsx
@@ -806,12 +806,12 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>【2026年】半導体市場の動向予測！世界や日本のシェア率、取り組みはどうなるのか？</t>
+          <t>AI半導体を巡る動き継続、一方AI不安も：Nvidia好業績他、メタも自社半導体に積極投資</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -845,23 +845,23 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2026 先端／注目半導体関連市場の現状と将来展望（市場調査レポート）</t>
+          <t>NEDOの公募事業に採択された次世代半導体の設計技術開発プロジェクトにキヤノンが参画</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C4" s="15" t="n"/>
       <c r="D4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="E4" s="15" t="n"/>
       <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
+      <c r="G4" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" s="15" t="n"/>
       <c r="I4" s="15" t="n"/>
       <c r="J4" s="15" t="n"/>
@@ -876,7 +876,9 @@
       <c r="S4" s="15" t="n"/>
       <c r="T4" s="15" t="n"/>
       <c r="U4" s="15" t="n"/>
-      <c r="V4" s="15" t="n"/>
+      <c r="V4" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="W4" s="15" t="n"/>
       <c r="X4" s="15" t="n"/>
       <c r="Y4" s="15" t="n"/>
@@ -884,28 +886,24 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>半導体市場の動向と規模 — AI需要に牽引される高成長期の展望</t>
+          <t>2026年3月期第3四半期 国内半導体装置メーカー業績まとめ：増収増益は7社中2社</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="12" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="F5" s="11" t="n"/>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n"/>
       <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="11" t="n"/>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -914,23 +912,27 @@
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
-      <c r="S5" s="11" t="n"/>
+      <c r="S5" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="T5" s="11" t="n"/>
       <c r="U5" s="11" t="n"/>
       <c r="V5" s="11" t="n"/>
       <c r="W5" s="11" t="n"/>
-      <c r="X5" s="11" t="n"/>
+      <c r="X5" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>日本の半導体市場規模、2034年までに632億米ドルに到達――年平均成長率（CAGR）4.40%で拡大</t>
+          <t>「世界の半導体、26年にも1兆ドル市場に」SEMIジャパン代表が予測</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C6" s="15" t="n"/>
@@ -946,9 +948,7 @@
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
-      <c r="L6" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
@@ -966,28 +966,30 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026年の半導体の転換点：業界リーダーが注目すべき5つの傾向</t>
+          <t>仰天！メモリ価格が2026年第1四半期に予想外の前期比倍増で過去最高の上昇率</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="11" t="n"/>
+      <c r="E7" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="11" t="n"/>
       <c r="G7" s="11" t="n"/>
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
+      <c r="L7" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
@@ -1005,12 +1007,12 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>世界半導体製造装置の2025年末市場予測発表 半導体製造装置市場は2027年に過去最高の1,560億ドルへ到達</t>
+          <t>ローム株がストップ高買い気配、デンソーが1.3兆円で買収提案と報道</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C8" s="15" t="n"/>
@@ -1021,7 +1023,9 @@
       <c r="F8" s="15" t="n"/>
       <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
+      <c r="I8" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
@@ -1031,41 +1035,41 @@
       <c r="P8" s="15" t="n"/>
       <c r="Q8" s="15" t="n"/>
       <c r="R8" s="15" t="n"/>
-      <c r="S8" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="S8" s="15" t="n"/>
       <c r="T8" s="15" t="n"/>
-      <c r="U8" s="15" t="n"/>
+      <c r="U8" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" s="15" t="n"/>
       <c r="W8" s="15" t="n"/>
-      <c r="X8" s="15" t="n"/>
+      <c r="X8" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026年、半導体需要の牽引役に変化か 世界半導体市場統計を読み解く</t>
+          <t>デンソーローム買収が提案された速報と半導体再編戦略を徹底解説</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="I9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11" t="n"/>
       <c r="K9" s="11" t="n"/>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
@@ -1076,7 +1080,9 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="11" t="n"/>
       <c r="T9" s="11" t="n"/>
-      <c r="U9" s="11" t="n"/>
+      <c r="U9" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="V9" s="11" t="n"/>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="11" t="n"/>
@@ -1085,30 +1091,28 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>半導体の日本市場（2026年～2034年）、市場規模（メモリデバイス、ロジックデバイス、アナログIC）・分析レポートを発表</t>
+          <t>【チームJAPAN】ラピダスがNTTやトヨタ、ソフトバンクなど32社と政府から2676億円資金調達</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C10" s="15" t="n"/>
       <c r="D10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
-      <c r="L10" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
@@ -1117,7 +1121,9 @@
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="15" t="n"/>
       <c r="T10" s="15" t="n"/>
-      <c r="U10" s="15" t="n"/>
+      <c r="U10" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" s="15" t="n"/>
       <c r="W10" s="15" t="n"/>
       <c r="X10" s="15" t="n"/>
@@ -1126,19 +1132,21 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>半導体株の買い時はいつ？AIバブルと2026年相場の分岐点を徹底分析</t>
+          <t>1月の世界半導体販売高、AI市況の増勢続く；MWC 2026モバイルデバイス最新動向</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="11" t="n"/>
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n"/>
@@ -1153,26 +1161,26 @@
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="11" t="n"/>
+      <c r="R11" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="S11" s="11" t="n"/>
       <c r="T11" s="11" t="n"/>
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="11" t="n"/>
       <c r="W11" s="11" t="n"/>
-      <c r="X11" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X11" s="11" t="n"/>
       <c r="Y11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>【業界必読】2026年の半導体「7大予測」、エヌビディア「一強」はいつまで続くのか</t>
+          <t>エヌビディア、元OpenAIムラティ氏の新興企業に出資－半導体を供給へ</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C12" s="15" t="n"/>
@@ -1197,23 +1205,23 @@
       <c r="R12" s="15" t="n"/>
       <c r="S12" s="15" t="n"/>
       <c r="T12" s="15" t="n"/>
-      <c r="U12" s="15" t="n"/>
+      <c r="U12" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V12" s="15" t="n"/>
       <c r="W12" s="15" t="n"/>
-      <c r="X12" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X12" s="15" t="n"/>
       <c r="Y12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>半導体株の買い時はいつ？AIバブルと2026年相場の分岐点を徹底分析（AI半導体投資特集）</t>
+          <t>NVIDIA「GTC」開幕へ、見どころはフィジカルAIや次世代半導体「Vera Rubin」</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
@@ -1236,84 +1244,84 @@
       <c r="P13" s="11" t="n"/>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n"/>
+      <c r="S13" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="T13" s="11" t="n"/>
       <c r="U13" s="11" t="n"/>
       <c r="V13" s="11" t="n"/>
       <c r="W13" s="11" t="n"/>
-      <c r="X13" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X13" s="11" t="n"/>
       <c r="Y13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026年の有望銘柄を探る（2）～「AI進化」が追い風？主役候補の日本株8選</t>
+          <t>半導体材料のJSR、業界再編の意欲に薄れ 本業磨き負債圧縮を優先</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="16" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15" t="n"/>
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="15" t="n"/>
       <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="15" t="n"/>
-      <c r="J14" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
-      <c r="P14" s="15" t="n"/>
+      <c r="P14" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="15" t="n"/>
       <c r="T14" s="15" t="n"/>
-      <c r="U14" s="15" t="n"/>
+      <c r="U14" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V14" s="15" t="n"/>
       <c r="W14" s="15" t="n"/>
-      <c r="X14" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X14" s="15" t="n"/>
       <c r="Y14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026年の半導体市場1.3兆ドル予測の裏側、AI偏重とメモリの高騰が生む市場の二極化</t>
+          <t>日本の半導体市場だけ8カ月間連続マイナス成長、世界市場は前年比46%増の中で孤立</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
-      <c r="J15" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="J15" s="11" t="n"/>
       <c r="K15" s="11" t="n"/>
-      <c r="L15" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
@@ -1331,12 +1339,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026年の半導体市場を占う10の注目トピック：大山聡の業界スコープ（96）</t>
+          <t>NVIDIAがAIエージェント必須半導体、性能35倍 受注残は159兆円に拡大</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C16" s="15" t="n"/>
@@ -1364,28 +1372,32 @@
       <c r="U16" s="15" t="n"/>
       <c r="V16" s="15" t="n"/>
       <c r="W16" s="15" t="n"/>
-      <c r="X16" s="15" t="n"/>
+      <c r="X16" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>AI投資拡大で注目！半導体関連日本株8選</t>
+          <t>米国政権インパクト半導体関連；AIでの板挟み(米中規制と倫理問題)の現状整理</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="12" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="H17" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="12" t="n">
         <v>1</v>
@@ -1399,26 +1411,22 @@
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="11" t="n"/>
-      <c r="T17" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="11" t="n"/>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="11" t="n"/>
       <c r="W17" s="11" t="n"/>
-      <c r="X17" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X17" s="11" t="n"/>
       <c r="Y17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>AI相場で株価変貌の前夜、「半導体材料」関連・大化けの系譜6銘柄</t>
+          <t>エヌビディア、2027年末までのAI半導体売上高1兆ドル以上見込む GTC基調講演で発表</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C18" s="15" t="n"/>
@@ -1438,9 +1446,7 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
       <c r="R18" s="15" t="n"/>
       <c r="S18" s="15" t="n"/>
@@ -1456,12 +1462,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>【2026年】半導体市場の動向予測！AI需要が牽引するシェア争いと日本の展略</t>
+          <t>NVIDIA、GTC 2026で「NemoClaw」発表 OpenClawを1コマンドで導入・安全に実行可能に</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C19" s="11" t="n"/>
@@ -1495,12 +1501,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>生成AI×半導体、26年も投資熱 アジア市場関係者に注目銘柄聞く</t>
+          <t>【速報】NVIDIA GTC 2026 Keynote Session（基調講演）レポート：Vera Rubin発表</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C20" s="15" t="n"/>
@@ -1523,27 +1529,25 @@
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="n"/>
-      <c r="T20" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="S20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="15" t="n"/>
       <c r="U20" s="15" t="n"/>
       <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
-      <c r="X20" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>四半期大幅増益の中小型半導体関連7銘柄</t>
+          <t>2026年春闘、大手は「ほぼ満額」 日立・NECなど半導体・電機5社の賃上げ結果まとめ</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C21" s="11" t="n"/>
@@ -1568,21 +1572,21 @@
       <c r="T21" s="11" t="n"/>
       <c r="U21" s="11" t="n"/>
       <c r="V21" s="11" t="n"/>
-      <c r="W21" s="11" t="n"/>
-      <c r="X21" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="W21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="11" t="n"/>
       <c r="Y21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>【日本株】AIブームを支える半導体、「前工程」に不可欠な素材メーカーに注目</t>
+          <t>NVIDIA GTC 2026が示した「推論シフト」——AIチップ市場の勢力図はどう変わるのか</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C22" s="15" t="n"/>
@@ -1602,9 +1606,7 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
       <c r="S22" s="15" t="n"/>
@@ -1612,20 +1614,18 @@
       <c r="U22" s="15" t="n"/>
       <c r="V22" s="15" t="n"/>
       <c r="W22" s="15" t="n"/>
-      <c r="X22" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X22" s="15" t="n"/>
       <c r="Y22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026年3月期上期 国内半導体装置メーカー 業績まとめ：増収増益は7社中3社</t>
+          <t>NVIDIA GTC 2026 開発者向けまとめ──推論コスト1/10時代に備えるために知っておくべきこと</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C23" s="11" t="n"/>
@@ -1637,7 +1637,9 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
+      <c r="J23" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" s="11" t="n"/>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
@@ -1646,27 +1648,23 @@
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="n"/>
-      <c r="S23" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="S23" s="11" t="n"/>
       <c r="T23" s="11" t="n"/>
       <c r="U23" s="11" t="n"/>
       <c r="V23" s="11" t="n"/>
       <c r="W23" s="11" t="n"/>
-      <c r="X23" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X23" s="11" t="n"/>
       <c r="Y23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>決算：半導体製造装置1〜3月2ケタ増収 AI投資加速追い風、3四半期ぶりに</t>
+          <t>NVIDIA GTC 2026：ジェンスン・フアンが描く「1兆ドルのAI工場」時代とデータセンター革命</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C24" s="15" t="n"/>
@@ -1689,27 +1687,25 @@
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
-      <c r="S24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" s="15" t="n"/>
+      <c r="S24" s="15" t="n"/>
+      <c r="T24" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="15" t="n"/>
       <c r="W24" s="15" t="n"/>
-      <c r="X24" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X24" s="15" t="n"/>
       <c r="Y24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026年1月〜3月 半導体関連イベント＆決算発表スケジュールまとめ</t>
+          <t>Nvidia GTC 2026よりAI半導体関連；製品&amp;展望、H200再開、Vera Rubin詳細</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C25" s="11" t="n"/>
@@ -1721,34 +1717,38 @@
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
+      <c r="J25" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" s="11" t="n"/>
-      <c r="L25" s="11" t="n"/>
+      <c r="L25" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="n"/>
-      <c r="S25" s="11" t="n"/>
+      <c r="S25" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="T25" s="11" t="n"/>
       <c r="U25" s="11" t="n"/>
       <c r="V25" s="11" t="n"/>
       <c r="W25" s="11" t="n"/>
-      <c r="X25" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X25" s="11" t="n"/>
       <c r="Y25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>半導体装置メーカー 業績まとめ【2026年3月期第3四半期】</t>
+          <t>デンソー、ロームへの買収提案を正式表明「半導体で幅広い貢献可能」SiC戦略を説明</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C26" s="15" t="n"/>
@@ -1759,7 +1759,9 @@
       <c r="F26" s="15" t="n"/>
       <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
+      <c r="I26" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="J26" s="15" t="n"/>
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
@@ -1769,27 +1771,25 @@
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
-      <c r="S26" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="S26" s="15" t="n"/>
       <c r="T26" s="15" t="n"/>
-      <c r="U26" s="15" t="n"/>
+      <c r="U26" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V26" s="15" t="n"/>
       <c r="W26" s="15" t="n"/>
-      <c r="X26" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X26" s="15" t="n"/>
       <c r="Y26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>四半期大幅増益の中小型半導体関連7銘柄（2026年1月集計版）</t>
+          <t>パワー半導体再編なぜ今？デンソーのローム買収提案で機運高まる業界再編の背景</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C27" s="11" t="n"/>
@@ -1800,7 +1800,9 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="11" t="n"/>
       <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
+      <c r="I27" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="11" t="n"/>
       <c r="L27" s="11" t="n"/>
@@ -1812,23 +1814,23 @@
       <c r="R27" s="11" t="n"/>
       <c r="S27" s="11" t="n"/>
       <c r="T27" s="11" t="n"/>
-      <c r="U27" s="11" t="n"/>
+      <c r="U27" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="V27" s="11" t="n"/>
       <c r="W27" s="11" t="n"/>
-      <c r="X27" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X27" s="11" t="n"/>
       <c r="Y27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>【2026年第1四半期】半導体銘柄おすすめ5選</t>
+          <t>デンソーがロームに買収提案、パワー半導体新局面「親和性ある」と専門家が評価</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C28" s="15" t="n"/>
@@ -1839,10 +1841,10 @@
       <c r="F28" s="15" t="n"/>
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="I28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="15" t="n"/>
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
@@ -1853,23 +1855,23 @@
       <c r="R28" s="15" t="n"/>
       <c r="S28" s="15" t="n"/>
       <c r="T28" s="15" t="n"/>
-      <c r="U28" s="15" t="n"/>
+      <c r="U28" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V28" s="15" t="n"/>
       <c r="W28" s="15" t="n"/>
-      <c r="X28" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X28" s="15" t="n"/>
       <c r="Y28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>【投資家必読】半導体装置メーカー決算から見えてくる今後の市場展望</t>
+          <t>JSR、半導体材料に全集中 売上高2～3倍へ、後工程向け伸ばす 業界再編への意欲は後退</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C29" s="11" t="n"/>
@@ -1887,30 +1889,28 @@
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="n"/>
       <c r="O29" s="11" t="n"/>
-      <c r="P29" s="11" t="n"/>
+      <c r="P29" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q29" s="11" t="n"/>
       <c r="R29" s="11" t="n"/>
-      <c r="S29" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="S29" s="11" t="n"/>
       <c r="T29" s="11" t="n"/>
       <c r="U29" s="11" t="n"/>
       <c r="V29" s="11" t="n"/>
       <c r="W29" s="11" t="n"/>
-      <c r="X29" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X29" s="11" t="n"/>
       <c r="Y29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>2026年3月度【半導体ニュース総覧】今、業界で何が起きているのか？</t>
+          <t>デンソーによるローム買収提案——SiC垂直統合と1兆3000億円の戦略的必然性を分析</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C30" s="15" t="n"/>
@@ -1921,7 +1921,9 @@
       <c r="F30" s="15" t="n"/>
       <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
+      <c r="I30" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="J30" s="15" t="n"/>
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
@@ -1933,23 +1935,23 @@
       <c r="R30" s="15" t="n"/>
       <c r="S30" s="15" t="n"/>
       <c r="T30" s="15" t="n"/>
-      <c r="U30" s="15" t="n"/>
+      <c r="U30" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V30" s="15" t="n"/>
       <c r="W30" s="15" t="n"/>
       <c r="X30" s="15" t="n"/>
-      <c r="Y30" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>半導体装置10社、1～3月期は8社増収 パワー半導体は軟調</t>
+          <t>ラピダスへの新規出資、ホンダや富士通など24社 量産達成には「額が少ない」との声も</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C31" s="11" t="n"/>
@@ -1958,11 +1960,11 @@
       </c>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="H31" s="11" t="n"/>
-      <c r="I31" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="11" t="n"/>
       <c r="L31" s="11" t="n"/>
@@ -1972,27 +1974,25 @@
       <c r="P31" s="11" t="n"/>
       <c r="Q31" s="11" t="n"/>
       <c r="R31" s="11" t="n"/>
-      <c r="S31" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="S31" s="11" t="n"/>
       <c r="T31" s="11" t="n"/>
-      <c r="U31" s="11" t="n"/>
+      <c r="U31" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" s="11" t="n"/>
       <c r="W31" s="11" t="n"/>
-      <c r="X31" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X31" s="11" t="n"/>
       <c r="Y31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>【2026年】半導体市場の動向予測！シェア率と日本の取り組みを詳細分析</t>
+          <t>フォークシート技術による1nmプロセスを2031年までに量産へ、半導体微細化の最前線</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C32" s="15" t="n"/>
@@ -2004,9 +2004,7 @@
       <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="15" t="n"/>
-      <c r="J32" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="J32" s="15" t="n"/>
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -2015,7 +2013,9 @@
       <c r="P32" s="15" t="n"/>
       <c r="Q32" s="15" t="n"/>
       <c r="R32" s="15" t="n"/>
-      <c r="S32" s="15" t="n"/>
+      <c r="S32" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="T32" s="15" t="n"/>
       <c r="U32" s="15" t="n"/>
       <c r="V32" s="15" t="n"/>

--- a/output/MarketNews-202603.xlsx
+++ b/output/MarketNews-202603.xlsx
@@ -205,10 +205,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -806,46 +806,48 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>AI半導体を巡る動き継続、一方AI不安も：Nvidia好業績他、メタも自社半導体に積極投資</t>
+          <t>2026年3月期第3四半期 国内半導体装置メーカー 業績まとめ：増収増益は7社中2社</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="11" t="n"/>
-      <c r="U3" s="11" t="n"/>
-      <c r="V3" s="11" t="n"/>
-      <c r="W3" s="11" t="n"/>
-      <c r="X3" s="11" t="n"/>
-      <c r="Y3" s="11" t="n"/>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="12" t="n"/>
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="12" t="n"/>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n"/>
+      <c r="S3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="12" t="n"/>
+      <c r="U3" s="12" t="n"/>
+      <c r="V3" s="12" t="n"/>
+      <c r="W3" s="12" t="n"/>
+      <c r="X3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>NEDOの公募事業に採択された次世代半導体の設計技術開発プロジェクトにキヤノンが参画</t>
+          <t>ロームが半導体製造でインド新興と協業、タタに続き：26年からの後工程委託に向け</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
@@ -859,11 +861,11 @@
       </c>
       <c r="E4" s="15" t="n"/>
       <c r="F4" s="15" t="n"/>
-      <c r="G4" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="G4" s="15" t="n"/>
       <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
+      <c r="I4" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
       <c r="L4" s="15" t="n"/>
@@ -875,10 +877,10 @@
       <c r="R4" s="15" t="n"/>
       <c r="S4" s="15" t="n"/>
       <c r="T4" s="15" t="n"/>
-      <c r="U4" s="15" t="n"/>
-      <c r="V4" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="15" t="n"/>
       <c r="W4" s="15" t="n"/>
       <c r="X4" s="15" t="n"/>
       <c r="Y4" s="15" t="n"/>
@@ -886,7 +888,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026年3月期第3四半期 国内半導体装置メーカー業績まとめ：増収増益は7社中2社</t>
+          <t>「世界の半導体、26年にも1兆ドル市場に」SEMIジャパン代表</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -894,61 +896,59 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="11" t="n"/>
-      <c r="U5" s="11" t="n"/>
-      <c r="V5" s="11" t="n"/>
-      <c r="W5" s="11" t="n"/>
-      <c r="X5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="11" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="12" t="n"/>
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="12" t="n"/>
+      <c r="U5" s="12" t="n"/>
+      <c r="V5" s="12" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="12" t="n"/>
+      <c r="Y5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>「世界の半導体、26年にも1兆ドル市場に」SEMIジャパン代表が予測</t>
+          <t>次世代半導体、投資指数ランキング上位に 超低消費電力メモリーなど</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C6" s="15" t="n"/>
       <c r="D6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
-      <c r="L6" s="15" t="n"/>
+      <c r="L6" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="M6" s="15" t="n"/>
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
@@ -960,54 +960,56 @@
       <c r="U6" s="15" t="n"/>
       <c r="V6" s="15" t="n"/>
       <c r="W6" s="15" t="n"/>
-      <c r="X6" s="15" t="n"/>
+      <c r="X6" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>仰天！メモリ価格が2026年第1四半期に予想外の前期比倍増で過去最高の上昇率</t>
+          <t>エヌビディアなどのAI半導体、米政府が輸出規制案－全世界対象に</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="11" t="n"/>
-      <c r="U7" s="11" t="n"/>
-      <c r="V7" s="11" t="n"/>
-      <c r="W7" s="11" t="n"/>
-      <c r="X7" s="11" t="n"/>
-      <c r="Y7" s="11" t="n"/>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="12" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="12" t="n"/>
+      <c r="Y7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>ローム株がストップ高買い気配、デンソーが1.3兆円で買収提案と報道</t>
+          <t>国産半導体の売上高目標「2040年に40兆円」政府、最先端研究へ拠点</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -1021,11 +1023,11 @@
       </c>
       <c r="E8" s="15" t="n"/>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
@@ -1037,20 +1039,16 @@
       <c r="R8" s="15" t="n"/>
       <c r="S8" s="15" t="n"/>
       <c r="T8" s="15" t="n"/>
-      <c r="U8" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U8" s="15" t="n"/>
       <c r="V8" s="15" t="n"/>
       <c r="W8" s="15" t="n"/>
-      <c r="X8" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="X8" s="15" t="n"/>
       <c r="Y8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>デンソーローム買収が提案された速報と半導体再編戦略を徹底解説</t>
+          <t>米政府、同盟国へのAI半導体輸出も規制か？</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1058,45 +1056,45 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="11" t="n"/>
-      <c r="U9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="11" t="n"/>
-      <c r="W9" s="11" t="n"/>
-      <c r="X9" s="11" t="n"/>
-      <c r="Y9" s="11" t="n"/>
+      <c r="C9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="12" t="n"/>
+      <c r="U9" s="12" t="n"/>
+      <c r="V9" s="12" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="12" t="n"/>
+      <c r="Y9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>【チームJAPAN】ラピダスがNTTやトヨタ、ソフトバンクなど32社と政府から2676億円資金調達</t>
+          <t>トランプ政権、AI半導体の輸出規制案を撤回 輸出促進の方針と矛盾</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C10" s="15" t="n"/>
@@ -1105,12 +1103,14 @@
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
+      <c r="J10" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
@@ -1121,9 +1121,7 @@
       <c r="R10" s="15" t="n"/>
       <c r="S10" s="15" t="n"/>
       <c r="T10" s="15" t="n"/>
-      <c r="U10" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U10" s="15" t="n"/>
       <c r="V10" s="15" t="n"/>
       <c r="W10" s="15" t="n"/>
       <c r="X10" s="15" t="n"/>
@@ -1132,55 +1130,53 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>1月の世界半導体販売高、AI市況の増勢続く；MWC 2026モバイルデバイス最新動向</t>
+          <t>「再編待ったなし」のパワー半導体業界：電子機器設計</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="11" t="n"/>
-      <c r="T11" s="11" t="n"/>
-      <c r="U11" s="11" t="n"/>
-      <c r="V11" s="11" t="n"/>
-      <c r="W11" s="11" t="n"/>
-      <c r="X11" s="11" t="n"/>
-      <c r="Y11" s="11" t="n"/>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="12" t="n"/>
+      <c r="U11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="12" t="n"/>
+      <c r="Y11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>エヌビディア、元OpenAIムラティ氏の新興企業に出資－半導体を供給へ</t>
+          <t>東芝との協議やデンソー提案への対応、ロームが新声明</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C12" s="15" t="n"/>
@@ -1191,10 +1187,10 @@
       <c r="F12" s="15" t="n"/>
       <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="I12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -1216,80 +1212,78 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA「GTC」開幕へ、見どころはフィジカルAIや次世代半導体「Vera Rubin」</t>
+          <t>NY株ハイライト 波乱の3月、半導体株がソフト株に劣後 中東緊迫が影</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" s="11" t="n"/>
-      <c r="U13" s="11" t="n"/>
-      <c r="V13" s="11" t="n"/>
-      <c r="W13" s="11" t="n"/>
-      <c r="X13" s="11" t="n"/>
-      <c r="Y13" s="11" t="n"/>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="12" t="n"/>
+      <c r="V13" s="12" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>半導体材料のJSR、業界再編の意欲に薄れ 本業磨き負債圧縮を優先</t>
+          <t>米商務省、ＡＩ半導体輸出の新規則案を撤回 公表から約2週間で</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="15" t="n"/>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="15" t="n"/>
       <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
+      <c r="H14" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
+      <c r="J14" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
-      <c r="P14" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="P14" s="15" t="n"/>
       <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
       <c r="S14" s="15" t="n"/>
       <c r="T14" s="15" t="n"/>
-      <c r="U14" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U14" s="15" t="n"/>
       <c r="V14" s="15" t="n"/>
       <c r="W14" s="15" t="n"/>
       <c r="X14" s="15" t="n"/>
@@ -1298,53 +1292,53 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>日本の半導体市場だけ8カ月間連続マイナス成長、世界市場は前年比46%増の中で孤立</t>
+          <t>次世代パワー半導体「期待の5材料」の現在地――電子版2026年3月号</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="11" t="n"/>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="11" t="n"/>
-      <c r="T15" s="11" t="n"/>
-      <c r="U15" s="11" t="n"/>
-      <c r="V15" s="11" t="n"/>
-      <c r="W15" s="11" t="n"/>
-      <c r="X15" s="11" t="n"/>
-      <c r="Y15" s="11" t="n"/>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+      <c r="P15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="12" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="12" t="n"/>
+      <c r="U15" s="12" t="n"/>
+      <c r="V15" s="12" t="n"/>
+      <c r="W15" s="12" t="n"/>
+      <c r="X15" s="12" t="n"/>
+      <c r="Y15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>NVIDIAがAIエージェント必須半導体、性能35倍 受注残は159兆円に拡大</t>
+          <t>2026年3月期第3四半期 国内半導体商社 業績まとめ：増収増益は8社</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C16" s="15" t="n"/>
@@ -1356,9 +1350,7 @@
       <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="15" t="n"/>
-      <c r="J16" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -1380,53 +1372,53 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>米国政権インパクト半導体関連；AIでの板挟み(米中規制と倫理問題)の現状整理</t>
+          <t>【2026年3月23日】世界半導体・電子部品市場レポート：メモリ価格「Q1確定」後の需給激震とHBM生産枠の奪い合い</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="11" t="n"/>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="11" t="n"/>
-      <c r="T17" s="11" t="n"/>
-      <c r="U17" s="11" t="n"/>
-      <c r="V17" s="11" t="n"/>
-      <c r="W17" s="11" t="n"/>
-      <c r="X17" s="11" t="n"/>
-      <c r="Y17" s="11" t="n"/>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="12" t="n"/>
+      <c r="V17" s="12" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="12" t="n"/>
+      <c r="Y17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>エヌビディア、2027年末までのAI半導体売上高1兆ドル以上見込む GTC基調講演で発表</t>
+          <t>デンソー、ロームに対する株式取得提案を正式表明</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C18" s="15" t="n"/>
@@ -1437,10 +1429,10 @@
       <c r="F18" s="15" t="n"/>
       <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="I18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="15" t="n"/>
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -1451,7 +1443,9 @@
       <c r="R18" s="15" t="n"/>
       <c r="S18" s="15" t="n"/>
       <c r="T18" s="15" t="n"/>
-      <c r="U18" s="15" t="n"/>
+      <c r="U18" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V18" s="15" t="n"/>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="16" t="n">
@@ -1462,51 +1456,53 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA、GTC 2026で「NemoClaw」発表 OpenClawを1コマンドで導入・安全に実行可能に</t>
+          <t>半導体市場、26年大台1兆ドル けん引役と2兆ドルの道筋</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="11" t="n"/>
-      <c r="U19" s="11" t="n"/>
-      <c r="V19" s="11" t="n"/>
-      <c r="W19" s="11" t="n"/>
-      <c r="X19" s="11" t="n"/>
-      <c r="Y19" s="11" t="n"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="12" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n"/>
+      <c r="V19" s="12" t="n"/>
+      <c r="W19" s="12" t="n"/>
+      <c r="X19" s="12" t="n"/>
+      <c r="Y19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>【速報】NVIDIA GTC 2026 Keynote Session（基調講演）レポート：Vera Rubin発表</t>
+          <t>パワー半導体再編が本格化 ローム・東芝・三菱電機が協議開始へ</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C20" s="15" t="n"/>
@@ -1517,10 +1513,10 @@
       <c r="F20" s="15" t="n"/>
       <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="I20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
@@ -1529,11 +1525,11 @@
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="16" t="n">
-        <v>1</v>
-      </c>
+      <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n"/>
-      <c r="U20" s="15" t="n"/>
+      <c r="U20" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="15" t="n"/>
@@ -1542,51 +1538,53 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026年春闘、大手は「ほぼ満額」 日立・NECなど半導体・電機5社の賃上げ結果まとめ</t>
+          <t>「究極の半導体」ダイヤモンドを社会へ 動態展示も実現の早大発新興：Power Diamond Systems</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="11" t="n"/>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="11" t="n"/>
-      <c r="U21" s="11" t="n"/>
-      <c r="V21" s="11" t="n"/>
-      <c r="W21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" s="11" t="n"/>
-      <c r="Y21" s="11" t="n"/>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="12" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="12" t="n"/>
+      <c r="U21" s="12" t="n"/>
+      <c r="V21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="12" t="n"/>
+      <c r="X21" s="12" t="n"/>
+      <c r="Y21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>NVIDIA GTC 2026が示した「推論シフト」——AIチップ市場の勢力図はどう変わるのか</t>
+          <t>原子1層の半導体から生じる光信号を40倍以上に増強、京大ら</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C22" s="15" t="n"/>
@@ -1598,10 +1596,10 @@
       <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
       <c r="I22" s="15" t="n"/>
-      <c r="J22" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
@@ -1612,7 +1610,9 @@
       <c r="S22" s="15" t="n"/>
       <c r="T22" s="15" t="n"/>
       <c r="U22" s="15" t="n"/>
-      <c r="V22" s="15" t="n"/>
+      <c r="V22" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="15" t="n"/>
       <c r="Y22" s="15" t="n"/>
@@ -1620,408 +1620,41 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA GTC 2026 開発者向けまとめ──推論コスト1/10時代に備えるために知っておくべきこと</t>
+          <t>2026年3月度【半導体ニュース総覧】今、業界で何が起きているのか?</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="11" t="n"/>
-      <c r="S23" s="11" t="n"/>
-      <c r="T23" s="11" t="n"/>
-      <c r="U23" s="11" t="n"/>
-      <c r="V23" s="11" t="n"/>
-      <c r="W23" s="11" t="n"/>
-      <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>NVIDIA GTC 2026：ジェンスン・フアンが描く「1兆ドルのAI工場」時代とデータセンター革命</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="15" t="n"/>
-      <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="n"/>
-      <c r="T24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="15" t="n"/>
-      <c r="V24" s="15" t="n"/>
-      <c r="W24" s="15" t="n"/>
-      <c r="X24" s="15" t="n"/>
-      <c r="Y24" s="15" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Nvidia GTC 2026よりAI半導体関連；製品&amp;展望、H200再開、Vera Rubin詳細</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="11" t="n"/>
-      <c r="S25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" s="11" t="n"/>
-      <c r="U25" s="11" t="n"/>
-      <c r="V25" s="11" t="n"/>
-      <c r="W25" s="11" t="n"/>
-      <c r="X25" s="11" t="n"/>
-      <c r="Y25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>デンソー、ロームへの買収提案を正式表明「半導体で幅広い貢献可能」SiC戦略を説明</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="15" t="n"/>
-      <c r="R26" s="15" t="n"/>
-      <c r="S26" s="15" t="n"/>
-      <c r="T26" s="15" t="n"/>
-      <c r="U26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="15" t="n"/>
-      <c r="W26" s="15" t="n"/>
-      <c r="X26" s="15" t="n"/>
-      <c r="Y26" s="15" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>パワー半導体再編なぜ今？デンソーのローム買収提案で機運高まる業界再編の背景</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="11" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="11" t="n"/>
-      <c r="U27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="11" t="n"/>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>デンソーがロームに買収提案、パワー半導体新局面「親和性ある」と専門家が評価</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="15" t="n"/>
-      <c r="Q28" s="15" t="n"/>
-      <c r="R28" s="15" t="n"/>
-      <c r="S28" s="15" t="n"/>
-      <c r="T28" s="15" t="n"/>
-      <c r="U28" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="15" t="n"/>
-      <c r="W28" s="15" t="n"/>
-      <c r="X28" s="15" t="n"/>
-      <c r="Y28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>JSR、半導体材料に全集中 売上高2～3倍へ、後工程向け伸ばす 業界再編への意欲は後退</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="11" t="n"/>
-      <c r="U29" s="11" t="n"/>
-      <c r="V29" s="11" t="n"/>
-      <c r="W29" s="11" t="n"/>
-      <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>デンソーによるローム買収提案——SiC垂直統合と1兆3000億円の戦略的必然性を分析</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="15" t="n"/>
-      <c r="Q30" s="15" t="n"/>
-      <c r="R30" s="15" t="n"/>
-      <c r="S30" s="15" t="n"/>
-      <c r="T30" s="15" t="n"/>
-      <c r="U30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="15" t="n"/>
-      <c r="W30" s="15" t="n"/>
-      <c r="X30" s="15" t="n"/>
-      <c r="Y30" s="15" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>ラピダスへの新規出資、ホンダや富士通など24社 量産達成には「額が少ない」との声も</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="11" t="n"/>
-      <c r="U31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="11" t="n"/>
-      <c r="W31" s="11" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="11" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>フォークシート技術による1nmプロセスを2031年までに量産へ、半導体微細化の最前線</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="15" t="n"/>
-      <c r="Q32" s="15" t="n"/>
-      <c r="R32" s="15" t="n"/>
-      <c r="S32" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" s="15" t="n"/>
-      <c r="U32" s="15" t="n"/>
-      <c r="V32" s="15" t="n"/>
-      <c r="W32" s="15" t="n"/>
-      <c r="X32" s="15" t="n"/>
-      <c r="Y32" s="15" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="12" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="12" t="n"/>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="12" t="n"/>
+      <c r="W23" s="12" t="n"/>
+      <c r="X23" s="12" t="n"/>
+      <c r="Y23" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2055,15 +1688,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
